--- a/diseases/d173/2010-2014.xlsx
+++ b/diseases/d173/2010-2014.xlsx
@@ -12558,6 +12558,11 @@
       <c r="R62" t="n">
         <v>0</v>
       </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12570,12 +12575,22 @@
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR62" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS62" t="inlineStr"/>
       <c r="AT62" t="n">
         <v>0</v>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV62" t="inlineStr">
         <is>
@@ -16623,6 +16638,11 @@
       <c r="R83" t="n">
         <v>0</v>
       </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16635,12 +16655,22 @@
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR83" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS83" t="inlineStr"/>
       <c r="AT83" t="n">
         <v>0</v>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV83" t="inlineStr">
         <is>
@@ -16758,6 +16788,11 @@
       <c r="R84" t="n">
         <v>0</v>
       </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16770,12 +16805,22 @@
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR84" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS84" t="inlineStr"/>
       <c r="AT84" t="n">
         <v>0</v>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV84" t="inlineStr">
         <is>
@@ -16893,6 +16938,11 @@
       <c r="R85" t="n">
         <v>0</v>
       </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16905,12 +16955,22 @@
       </c>
       <c r="AP85" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR85" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS85" t="inlineStr"/>
       <c r="AT85" t="n">
         <v>0</v>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV85" t="inlineStr">
         <is>
@@ -17028,6 +17088,11 @@
       <c r="R86" t="n">
         <v>0</v>
       </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17040,12 +17105,22 @@
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR86" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS86" t="inlineStr"/>
       <c r="AT86" t="n">
         <v>0</v>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV86" t="inlineStr">
         <is>
@@ -17163,6 +17238,11 @@
       <c r="R87" t="n">
         <v>0</v>
       </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17175,12 +17255,22 @@
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR87" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS87" t="inlineStr"/>
       <c r="AT87" t="n">
         <v>0</v>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV87" t="inlineStr">
         <is>
@@ -17298,6 +17388,11 @@
       <c r="R88" t="n">
         <v>0</v>
       </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17310,12 +17405,22 @@
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR88" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS88" t="inlineStr"/>
       <c r="AT88" t="n">
         <v>0</v>
+      </c>
+      <c r="AU88" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV88" t="inlineStr">
         <is>
@@ -17433,6 +17538,11 @@
       <c r="R89" t="n">
         <v>0</v>
       </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17445,12 +17555,22 @@
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR89" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS89" t="inlineStr"/>
       <c r="AT89" t="n">
         <v>0</v>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV89" t="inlineStr">
         <is>
@@ -17568,6 +17688,11 @@
       <c r="R90" t="n">
         <v>0</v>
       </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17580,12 +17705,22 @@
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR90" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS90" t="inlineStr"/>
       <c r="AT90" t="n">
         <v>0</v>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV90" t="inlineStr">
         <is>
@@ -17703,6 +17838,11 @@
       <c r="R91" t="n">
         <v>0</v>
       </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17715,12 +17855,22 @@
       </c>
       <c r="AP91" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR91" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS91" t="inlineStr"/>
       <c r="AT91" t="n">
         <v>0</v>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV91" t="inlineStr">
         <is>
@@ -17838,6 +17988,11 @@
       <c r="R92" t="n">
         <v>0</v>
       </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17850,12 +18005,22 @@
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR92" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS92" t="inlineStr"/>
       <c r="AT92" t="n">
         <v>0</v>
+      </c>
+      <c r="AU92" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV92" t="inlineStr">
         <is>
@@ -17973,6 +18138,11 @@
       <c r="R93" t="n">
         <v>0</v>
       </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17985,12 +18155,22 @@
       </c>
       <c r="AP93" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR93" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS93" t="inlineStr"/>
       <c r="AT93" t="n">
         <v>0</v>
+      </c>
+      <c r="AU93" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV93" t="inlineStr">
         <is>
@@ -22431,6 +22611,11 @@
       <c r="R116" t="n">
         <v>0</v>
       </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22443,12 +22628,22 @@
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR116" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS116" t="inlineStr"/>
       <c r="AT116" t="n">
         <v>0</v>
+      </c>
+      <c r="AU116" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV116" t="inlineStr">
         <is>
@@ -26496,6 +26691,11 @@
       <c r="R137" t="n">
         <v>0</v>
       </c>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA137" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -26508,12 +26708,22 @@
       </c>
       <c r="AP137" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR137" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS137" t="inlineStr"/>
       <c r="AT137" t="n">
         <v>0</v>
+      </c>
+      <c r="AU137" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV137" t="inlineStr">
         <is>
@@ -26631,6 +26841,11 @@
       <c r="R138" t="n">
         <v>0</v>
       </c>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA138" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -26643,12 +26858,22 @@
       </c>
       <c r="AP138" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR138" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS138" t="inlineStr"/>
       <c r="AT138" t="n">
         <v>0</v>
+      </c>
+      <c r="AU138" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV138" t="inlineStr">
         <is>
@@ -26766,6 +26991,11 @@
       <c r="R139" t="n">
         <v>0</v>
       </c>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA139" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -26778,12 +27008,22 @@
       </c>
       <c r="AP139" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR139" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS139" t="inlineStr"/>
       <c r="AT139" t="n">
         <v>0</v>
+      </c>
+      <c r="AU139" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV139" t="inlineStr">
         <is>
@@ -26901,6 +27141,11 @@
       <c r="R140" t="n">
         <v>0</v>
       </c>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA140" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -26913,12 +27158,22 @@
       </c>
       <c r="AP140" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR140" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS140" t="inlineStr"/>
       <c r="AT140" t="n">
         <v>0</v>
+      </c>
+      <c r="AU140" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV140" t="inlineStr">
         <is>
@@ -27036,6 +27291,11 @@
       <c r="R141" t="n">
         <v>0</v>
       </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA141" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -27048,12 +27308,22 @@
       </c>
       <c r="AP141" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR141" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS141" t="inlineStr"/>
       <c r="AT141" t="n">
         <v>0</v>
+      </c>
+      <c r="AU141" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV141" t="inlineStr">
         <is>
@@ -27171,6 +27441,11 @@
       <c r="R142" t="n">
         <v>0</v>
       </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA142" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -27183,12 +27458,22 @@
       </c>
       <c r="AP142" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR142" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS142" t="inlineStr"/>
       <c r="AT142" t="n">
         <v>0</v>
+      </c>
+      <c r="AU142" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV142" t="inlineStr">
         <is>
@@ -27306,6 +27591,11 @@
       <c r="R143" t="n">
         <v>0</v>
       </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA143" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -27318,12 +27608,22 @@
       </c>
       <c r="AP143" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR143" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS143" t="inlineStr"/>
       <c r="AT143" t="n">
         <v>0</v>
+      </c>
+      <c r="AU143" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV143" t="inlineStr">
         <is>
@@ -27441,6 +27741,11 @@
       <c r="R144" t="n">
         <v>0</v>
       </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA144" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -27453,12 +27758,22 @@
       </c>
       <c r="AP144" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR144" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS144" t="inlineStr"/>
       <c r="AT144" t="n">
         <v>0</v>
+      </c>
+      <c r="AU144" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV144" t="inlineStr">
         <is>
@@ -28017,6 +28332,11 @@
       <c r="R148" t="n">
         <v>0</v>
       </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA148" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -28029,12 +28349,22 @@
       </c>
       <c r="AP148" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR148" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS148" t="inlineStr"/>
       <c r="AT148" t="n">
         <v>0</v>
+      </c>
+      <c r="AU148" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV148" t="inlineStr">
         <is>
@@ -28740,6 +29070,11 @@
       <c r="R153" t="n">
         <v>0</v>
       </c>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA153" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -28752,12 +29087,22 @@
       </c>
       <c r="AP153" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR153" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS153" t="inlineStr"/>
       <c r="AT153" t="n">
         <v>0</v>
+      </c>
+      <c r="AU153" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV153" t="inlineStr">
         <is>
@@ -29463,6 +29808,11 @@
       <c r="R158" t="n">
         <v>0</v>
       </c>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA158" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -29475,12 +29825,22 @@
       </c>
       <c r="AP158" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR158" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS158" t="inlineStr"/>
       <c r="AT158" t="n">
         <v>0</v>
+      </c>
+      <c r="AU158" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV158" t="inlineStr">
         <is>
@@ -34656,6 +35016,11 @@
       <c r="R186" t="n">
         <v>0</v>
       </c>
+      <c r="S186" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA186" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -34668,12 +35033,22 @@
       </c>
       <c r="AP186" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR186" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS186" t="inlineStr"/>
       <c r="AT186" t="n">
         <v>0</v>
+      </c>
+      <c r="AU186" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV186" t="inlineStr">
         <is>
@@ -39309,6 +39684,11 @@
       <c r="R211" t="n">
         <v>0</v>
       </c>
+      <c r="S211" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA211" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -39321,12 +39701,22 @@
       </c>
       <c r="AP211" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR211" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS211" t="inlineStr"/>
       <c r="AT211" t="n">
         <v>0</v>
+      </c>
+      <c r="AU211" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV211" t="inlineStr">
         <is>
@@ -40032,6 +40422,11 @@
       <c r="R216" t="n">
         <v>0</v>
       </c>
+      <c r="S216" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA216" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -40044,12 +40439,22 @@
       </c>
       <c r="AP216" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR216" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS216" t="inlineStr"/>
       <c r="AT216" t="n">
         <v>0</v>
+      </c>
+      <c r="AU216" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV216" t="inlineStr">
         <is>
@@ -40902,6 +41307,11 @@
       <c r="R222" t="n">
         <v>0</v>
       </c>
+      <c r="S222" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA222" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -40914,12 +41324,22 @@
       </c>
       <c r="AP222" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR222" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS222" t="inlineStr"/>
       <c r="AT222" t="n">
         <v>0</v>
+      </c>
+      <c r="AU222" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV222" t="inlineStr">
         <is>
@@ -41625,6 +42045,11 @@
       <c r="R227" t="n">
         <v>0</v>
       </c>
+      <c r="S227" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA227" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -41637,12 +42062,22 @@
       </c>
       <c r="AP227" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR227" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS227" t="inlineStr"/>
       <c r="AT227" t="n">
         <v>0</v>
+      </c>
+      <c r="AU227" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV227" t="inlineStr">
         <is>
@@ -42348,6 +42783,11 @@
       <c r="R232" t="n">
         <v>0</v>
       </c>
+      <c r="S232" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA232" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -42360,12 +42800,22 @@
       </c>
       <c r="AP232" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR232" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS232" t="inlineStr"/>
       <c r="AT232" t="n">
         <v>0</v>
+      </c>
+      <c r="AU232" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV232" t="inlineStr">
         <is>
@@ -43218,6 +43668,11 @@
       <c r="R238" t="n">
         <v>0</v>
       </c>
+      <c r="S238" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA238" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -43230,12 +43685,22 @@
       </c>
       <c r="AP238" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR238" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS238" t="inlineStr"/>
       <c r="AT238" t="n">
         <v>0</v>
+      </c>
+      <c r="AU238" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV238" t="inlineStr">
         <is>
@@ -43941,6 +44406,11 @@
       <c r="R243" t="n">
         <v>0</v>
       </c>
+      <c r="S243" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA243" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -43953,12 +44423,22 @@
       </c>
       <c r="AP243" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR243" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS243" t="inlineStr"/>
       <c r="AT243" t="n">
         <v>0</v>
+      </c>
+      <c r="AU243" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV243" t="inlineStr">
         <is>
@@ -44811,6 +45291,11 @@
       <c r="R249" t="n">
         <v>0</v>
       </c>
+      <c r="S249" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA249" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -44823,12 +45308,22 @@
       </c>
       <c r="AP249" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR249" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS249" t="inlineStr"/>
       <c r="AT249" t="n">
         <v>0</v>
+      </c>
+      <c r="AU249" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV249" t="inlineStr">
         <is>
@@ -45534,6 +46029,11 @@
       <c r="R254" t="n">
         <v>0</v>
       </c>
+      <c r="S254" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA254" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -45546,12 +46046,22 @@
       </c>
       <c r="AP254" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR254" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS254" t="inlineStr"/>
       <c r="AT254" t="n">
         <v>0</v>
+      </c>
+      <c r="AU254" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV254" t="inlineStr">
         <is>
@@ -46257,6 +46767,11 @@
       <c r="R259" t="n">
         <v>0</v>
       </c>
+      <c r="S259" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA259" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -46269,12 +46784,22 @@
       </c>
       <c r="AP259" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR259" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS259" t="inlineStr"/>
       <c r="AT259" t="n">
         <v>0</v>
+      </c>
+      <c r="AU259" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV259" t="inlineStr">
         <is>
@@ -47127,6 +47652,11 @@
       <c r="R265" t="n">
         <v>0</v>
       </c>
+      <c r="S265" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA265" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -47139,12 +47669,22 @@
       </c>
       <c r="AP265" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR265" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS265" t="inlineStr"/>
       <c r="AT265" t="n">
         <v>0</v>
+      </c>
+      <c r="AU265" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV265" t="inlineStr">
         <is>
@@ -52173,6 +52713,11 @@
       <c r="R292" t="n">
         <v>0</v>
       </c>
+      <c r="S292" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA292" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -52185,12 +52730,22 @@
       </c>
       <c r="AP292" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR292" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS292" t="inlineStr"/>
       <c r="AT292" t="n">
         <v>0</v>
+      </c>
+      <c r="AU292" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV292" t="inlineStr">
         <is>
@@ -56826,6 +57381,11 @@
       <c r="R317" t="n">
         <v>0</v>
       </c>
+      <c r="S317" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA317" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -56838,12 +57398,22 @@
       </c>
       <c r="AP317" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR317" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS317" t="inlineStr"/>
       <c r="AT317" t="n">
         <v>0</v>
+      </c>
+      <c r="AU317" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV317" t="inlineStr">
         <is>
@@ -57549,6 +58119,11 @@
       <c r="R322" t="n">
         <v>0</v>
       </c>
+      <c r="S322" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA322" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -57561,12 +58136,22 @@
       </c>
       <c r="AP322" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR322" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS322" t="inlineStr"/>
       <c r="AT322" t="n">
         <v>0</v>
+      </c>
+      <c r="AU322" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV322" t="inlineStr">
         <is>
@@ -58419,6 +59004,11 @@
       <c r="R328" t="n">
         <v>0</v>
       </c>
+      <c r="S328" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA328" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -58431,12 +59021,22 @@
       </c>
       <c r="AP328" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR328" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS328" t="inlineStr"/>
       <c r="AT328" t="n">
         <v>0</v>
+      </c>
+      <c r="AU328" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV328" t="inlineStr">
         <is>
@@ -59142,6 +59742,11 @@
       <c r="R333" t="n">
         <v>0</v>
       </c>
+      <c r="S333" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA333" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -59154,12 +59759,22 @@
       </c>
       <c r="AP333" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR333" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS333" t="inlineStr"/>
       <c r="AT333" t="n">
         <v>0</v>
+      </c>
+      <c r="AU333" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV333" t="inlineStr">
         <is>
@@ -60012,6 +60627,11 @@
       <c r="R339" t="n">
         <v>0</v>
       </c>
+      <c r="S339" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA339" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -60024,12 +60644,22 @@
       </c>
       <c r="AP339" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR339" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS339" t="inlineStr"/>
       <c r="AT339" t="n">
         <v>0</v>
+      </c>
+      <c r="AU339" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV339" t="inlineStr">
         <is>
@@ -60735,6 +61365,11 @@
       <c r="R344" t="n">
         <v>0</v>
       </c>
+      <c r="S344" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA344" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -60747,12 +61382,22 @@
       </c>
       <c r="AP344" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR344" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS344" t="inlineStr"/>
       <c r="AT344" t="n">
         <v>0</v>
+      </c>
+      <c r="AU344" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV344" t="inlineStr">
         <is>
@@ -61458,6 +62103,11 @@
       <c r="R349" t="n">
         <v>0</v>
       </c>
+      <c r="S349" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA349" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -61470,12 +62120,22 @@
       </c>
       <c r="AP349" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR349" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS349" t="inlineStr"/>
       <c r="AT349" t="n">
         <v>0</v>
+      </c>
+      <c r="AU349" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV349" t="inlineStr">
         <is>
@@ -62328,6 +62988,11 @@
       <c r="R355" t="n">
         <v>0</v>
       </c>
+      <c r="S355" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA355" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -62340,12 +63005,22 @@
       </c>
       <c r="AP355" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR355" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS355" t="inlineStr"/>
       <c r="AT355" t="n">
         <v>0</v>
+      </c>
+      <c r="AU355" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV355" t="inlineStr">
         <is>
@@ -63051,6 +63726,11 @@
       <c r="R360" t="n">
         <v>0</v>
       </c>
+      <c r="S360" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA360" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -63063,12 +63743,22 @@
       </c>
       <c r="AP360" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR360" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS360" t="inlineStr"/>
       <c r="AT360" t="n">
         <v>0</v>
+      </c>
+      <c r="AU360" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV360" t="inlineStr">
         <is>
@@ -63774,6 +64464,11 @@
       <c r="R365" t="n">
         <v>0</v>
       </c>
+      <c r="S365" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA365" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -63786,12 +64481,22 @@
       </c>
       <c r="AP365" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR365" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS365" t="inlineStr"/>
       <c r="AT365" t="n">
         <v>0</v>
+      </c>
+      <c r="AU365" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV365" t="inlineStr">
         <is>
@@ -64644,6 +65349,11 @@
       <c r="R371" t="n">
         <v>0</v>
       </c>
+      <c r="S371" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA371" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -64656,12 +65366,22 @@
       </c>
       <c r="AP371" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR371" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS371" t="inlineStr"/>
       <c r="AT371" t="n">
         <v>0</v>
+      </c>
+      <c r="AU371" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV371" t="inlineStr">
         <is>
